--- a/data/trans_orig/P16A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74219</t>
+          <t>72358</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108345</t>
+          <t>108689</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>203297</t>
+          <t>201916</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>260261</t>
+          <t>256261</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>284794</t>
+          <t>286055</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>349734</t>
+          <t>355043</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>923378</t>
+          <t>923034</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>957504</t>
+          <t>959365</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1054852</t>
+          <t>1058852</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1111816</t>
+          <t>1113197</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1997101</t>
+          <t>1991792</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2062041</t>
+          <t>2060780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37403</t>
+          <t>37720</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65347</t>
+          <t>64674</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98214</t>
+          <t>100513</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>139764</t>
+          <t>140221</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>145821</t>
+          <t>144356</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>194977</t>
+          <t>195324</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1628066</t>
+          <t>1628739</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1656010</t>
+          <t>1655693</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1447909</t>
+          <t>1447452</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1489459</t>
+          <t>1487160</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3086109</t>
+          <t>3085762</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3135265</t>
+          <t>3136730</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>31772</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20322</t>
+          <t>20413</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41156</t>
+          <t>40326</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38006</t>
+          <t>37922</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66148</t>
+          <t>66864</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520158</t>
+          <t>519636</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>538112</t>
+          <t>538881</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>435256</t>
+          <t>436086</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456090</t>
+          <t>455999</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>961672</t>
+          <t>960956</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>989814</t>
+          <t>989898</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>137978</t>
+          <t>137711</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>188322</t>
+          <t>186644</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>341295</t>
+          <t>339971</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>413853</t>
+          <t>408540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>495709</t>
+          <t>499543</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>588787</t>
+          <t>582131</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3088221</t>
+          <t>3089899</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3138565</t>
+          <t>3138832</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2965344</t>
+          <t>2970657</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3037902</t>
+          <t>3039226</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6066954</t>
+          <t>6073610</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6160032</t>
+          <t>6156198</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90038</t>
+          <t>87705</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>132616</t>
+          <t>128142</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>300747</t>
+          <t>296353</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>364330</t>
+          <t>365049</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>402579</t>
+          <t>402505</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>478259</t>
+          <t>481934</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>842027</t>
+          <t>846501</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>884605</t>
+          <t>886938</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>973467</t>
+          <t>972748</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1037050</t>
+          <t>1041444</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1834181</t>
+          <t>1830506</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1909861</t>
+          <t>1909935</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75237</t>
+          <t>76958</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115918</t>
+          <t>117847</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>170620</t>
+          <t>170728</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>224291</t>
+          <t>224140</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>258249</t>
+          <t>259065</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>328004</t>
+          <t>324719</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1848039</t>
+          <t>1846110</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1888720</t>
+          <t>1886999</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1533512</t>
+          <t>1533663</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1587183</t>
+          <t>1587075</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3393756</t>
+          <t>3397041</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3463511</t>
+          <t>3462695</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13491</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37544</t>
+          <t>35726</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17998</t>
+          <t>17922</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40429</t>
+          <t>39488</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37675</t>
+          <t>37825</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70679</t>
+          <t>68262</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>443637</t>
+          <t>445455</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>467690</t>
+          <t>467961</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>418202</t>
+          <t>419143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>440633</t>
+          <t>440709</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>869134</t>
+          <t>871551</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>902138</t>
+          <t>901988</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>195611</t>
+          <t>197351</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>258811</t>
+          <t>259778</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>509919</t>
+          <t>512767</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>601067</t>
+          <t>597227</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>719190</t>
+          <t>727853</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>833413</t>
+          <t>837201</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3160971</t>
+          <t>3160004</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3224171</t>
+          <t>3222431</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2953163</t>
+          <t>2957003</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3044311</t>
+          <t>3041463</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6140599</t>
+          <t>6136811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6254822</t>
+          <t>6246159</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,56%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67629</t>
+          <t>66592</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>100478</t>
+          <t>101028</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>227825</t>
+          <t>225276</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>281746</t>
+          <t>284686</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>303078</t>
+          <t>305392</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>372499</t>
+          <t>370880</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>653869</t>
+          <t>653319</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>686718</t>
+          <t>687755</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>712914</t>
+          <t>709974</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>766835</t>
+          <t>769384</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1376508</t>
+          <t>1378127</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1445929</t>
+          <t>1443615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,54%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87633</t>
+          <t>88152</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128864</t>
+          <t>129476</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>218557</t>
+          <t>219899</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>276760</t>
+          <t>281469</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>318539</t>
+          <t>316664</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>392746</t>
+          <t>391820</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1947521</t>
+          <t>1946909</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1988752</t>
+          <t>1988233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1711540</t>
+          <t>1706831</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1769743</t>
+          <t>1768401</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3671939</t>
+          <t>3672865</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3746146</t>
+          <t>3748021</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,21%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>13499</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33305</t>
+          <t>32451</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23080</t>
+          <t>22832</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47510</t>
+          <t>48514</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40722</t>
+          <t>41055</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72339</t>
+          <t>71693</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>513581</t>
+          <t>514435</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534228</t>
+          <t>533387</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>501630</t>
+          <t>500626</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>526060</t>
+          <t>526308</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1023688</t>
+          <t>1024334</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1055305</t>
+          <t>1054972</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>184826</t>
+          <t>184321</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>241585</t>
+          <t>240273</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>493571</t>
+          <t>492334</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>580425</t>
+          <t>579417</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>692256</t>
+          <t>698697</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>800989</t>
+          <t>808029</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3136033</t>
+          <t>3137345</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3192792</t>
+          <t>3193297</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2951675</t>
+          <t>2952683</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3038529</t>
+          <t>3039766</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6108729</t>
+          <t>6101689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6217462</t>
+          <t>6211021</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79059</t>
+          <t>80425</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110993</t>
+          <t>112456</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>242213</t>
+          <t>240442</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>283921</t>
+          <t>282522</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>329725</t>
+          <t>328814</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>383153</t>
+          <t>379360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>403945</t>
+          <t>402482</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>435879</t>
+          <t>434513</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>471587</t>
+          <t>472986</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>513295</t>
+          <t>515066</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>887293</t>
+          <t>891086</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>940721</t>
+          <t>941632</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,12%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>105719</t>
+          <t>99742</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>179875</t>
+          <t>178854</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>201134</t>
+          <t>210534</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>328586</t>
+          <t>324229</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>339690</t>
+          <t>340825</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>487722</t>
+          <t>488322</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2110452</t>
+          <t>2111473</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2184608</t>
+          <t>2190585</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1909237</t>
+          <t>1913594</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2036689</t>
+          <t>2027289</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4040428</t>
+          <t>4039828</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4188460</t>
+          <t>4187325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28887</t>
+          <t>29474</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52190</t>
+          <t>53606</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48242</t>
+          <t>46844</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70881</t>
+          <t>71056</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82649</t>
+          <t>82377</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114134</t>
+          <t>115503</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>594433</t>
+          <t>593017</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>617736</t>
+          <t>617149</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>589582</t>
+          <t>589407</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>612221</t>
+          <t>613619</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1192952</t>
+          <t>1191583</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1224437</t>
+          <t>1224709</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>222511</t>
+          <t>217547</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>321920</t>
+          <t>319352</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>481978</t>
+          <t>483402</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>662028</t>
+          <t>655027</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>763101</t>
+          <t>765729</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>957660</t>
+          <t>956560</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3129969</t>
+          <t>3132537</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3229378</t>
+          <t>3234342</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2991766</t>
+          <t>2998767</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3171816</t>
+          <t>3170392</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6148023</t>
+          <t>6149123</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6342582</t>
+          <t>6339954</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72358</t>
+          <t>73646</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108689</t>
+          <t>108631</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>201916</t>
+          <t>201762</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>256261</t>
+          <t>259104</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>286055</t>
+          <t>284219</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>355043</t>
+          <t>351606</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>923034</t>
+          <t>923092</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>959365</t>
+          <t>958077</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1058852</t>
+          <t>1056009</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1113197</t>
+          <t>1113351</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1991792</t>
+          <t>1995229</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2060780</t>
+          <t>2062616</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37720</t>
+          <t>36386</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64674</t>
+          <t>65495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>100513</t>
+          <t>99458</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140221</t>
+          <t>141699</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>144356</t>
+          <t>146793</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>195324</t>
+          <t>198587</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1628739</t>
+          <t>1627918</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1655693</t>
+          <t>1657027</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1447452</t>
+          <t>1445974</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1487160</t>
+          <t>1488215</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3085762</t>
+          <t>3082499</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3136730</t>
+          <t>3134293</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12527</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31772</t>
+          <t>30511</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20413</t>
+          <t>20103</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40326</t>
+          <t>40403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37922</t>
+          <t>37004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66864</t>
+          <t>65389</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519636</t>
+          <t>520897</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>538881</t>
+          <t>538039</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>436086</t>
+          <t>436009</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455999</t>
+          <t>456309</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>960956</t>
+          <t>962431</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>989898</t>
+          <t>990816</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>137711</t>
+          <t>135663</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>186644</t>
+          <t>187471</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>339971</t>
+          <t>342761</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>408540</t>
+          <t>412231</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>499543</t>
+          <t>495382</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>582131</t>
+          <t>586238</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3089899</t>
+          <t>3089072</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3138832</t>
+          <t>3140880</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2970657</t>
+          <t>2966966</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3039226</t>
+          <t>3036436</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6073610</t>
+          <t>6069503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6156198</t>
+          <t>6160359</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87705</t>
+          <t>88704</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128142</t>
+          <t>131612</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>296353</t>
+          <t>301715</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>365049</t>
+          <t>364152</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>402505</t>
+          <t>399111</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>481934</t>
+          <t>475925</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>846501</t>
+          <t>843031</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>886938</t>
+          <t>885939</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>972748</t>
+          <t>973645</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1041444</t>
+          <t>1036082</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1830506</t>
+          <t>1836515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1909935</t>
+          <t>1913329</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,74%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76958</t>
+          <t>76103</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>117847</t>
+          <t>115282</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>170728</t>
+          <t>170784</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>224140</t>
+          <t>226181</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>259065</t>
+          <t>254111</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>324719</t>
+          <t>324283</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1846110</t>
+          <t>1848675</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1886999</t>
+          <t>1887854</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1533663</t>
+          <t>1531622</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1587075</t>
+          <t>1587019</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3397041</t>
+          <t>3397477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3462695</t>
+          <t>3467649</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13220</t>
+          <t>13026</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35726</t>
+          <t>36920</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17922</t>
+          <t>17919</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39488</t>
+          <t>40488</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37825</t>
+          <t>37884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68262</t>
+          <t>67817</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>445455</t>
+          <t>444261</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>467961</t>
+          <t>468155</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>419143</t>
+          <t>418143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>440709</t>
+          <t>440712</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>871551</t>
+          <t>871996</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>901988</t>
+          <t>901929</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>197351</t>
+          <t>195546</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>259778</t>
+          <t>260016</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>512767</t>
+          <t>507017</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>597227</t>
+          <t>598890</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>727853</t>
+          <t>724288</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>837201</t>
+          <t>839033</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3160004</t>
+          <t>3159766</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3222431</t>
+          <t>3224236</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2957003</t>
+          <t>2955340</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3041463</t>
+          <t>3047213</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6136811</t>
+          <t>6134979</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6246159</t>
+          <t>6249724</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66592</t>
+          <t>67950</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>101028</t>
+          <t>99630</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>225276</t>
+          <t>225559</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>284686</t>
+          <t>283717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>305392</t>
+          <t>304626</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>370880</t>
+          <t>369641</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>653319</t>
+          <t>654717</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>687755</t>
+          <t>686397</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>709974</t>
+          <t>710943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>769384</t>
+          <t>769101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1378127</t>
+          <t>1379366</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1443615</t>
+          <t>1444381</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,58%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88152</t>
+          <t>87996</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>129476</t>
+          <t>130411</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>219899</t>
+          <t>219713</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>281469</t>
+          <t>278482</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>316664</t>
+          <t>320301</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>391820</t>
+          <t>393669</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1946909</t>
+          <t>1945974</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1988233</t>
+          <t>1988389</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1706831</t>
+          <t>1709818</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1768401</t>
+          <t>1768587</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3672865</t>
+          <t>3671016</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3748021</t>
+          <t>3744384</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,12%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13499</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32451</t>
+          <t>32708</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22832</t>
+          <t>22955</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48514</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41055</t>
+          <t>39828</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71693</t>
+          <t>73485</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>514435</t>
+          <t>514178</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533387</t>
+          <t>533686</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>500626</t>
+          <t>502232</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>526308</t>
+          <t>526185</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1024334</t>
+          <t>1022542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1054972</t>
+          <t>1056199</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>184321</t>
+          <t>182632</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>240273</t>
+          <t>239783</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>492334</t>
+          <t>490598</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>579417</t>
+          <t>580699</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>698697</t>
+          <t>696971</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>808029</t>
+          <t>801868</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3137345</t>
+          <t>3137835</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3193297</t>
+          <t>3194986</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2952683</t>
+          <t>2951401</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3039766</t>
+          <t>3041502</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6101689</t>
+          <t>6107850</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6211021</t>
+          <t>6212747</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>93817</t>
+          <t>100923</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80425</t>
+          <t>85038</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112456</t>
+          <t>119392</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>261106</t>
+          <t>280074</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>240442</t>
+          <t>258078</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>282522</t>
+          <t>300348</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>354923</t>
+          <t>380997</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>328814</t>
+          <t>354250</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>379360</t>
+          <t>410127</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>421121</t>
+          <t>477606</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>402482</t>
+          <t>459137</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>434513</t>
+          <t>493491</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>494402</t>
+          <t>541964</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>472986</t>
+          <t>521690</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>515066</t>
+          <t>563960</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>915523</t>
+          <t>1019570</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>891086</t>
+          <t>990440</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>941632</t>
+          <t>1046317</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,71%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>149457</t>
+          <t>163430</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>99742</t>
+          <t>141858</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>178854</t>
+          <t>190535</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>281750</t>
+          <t>307161</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>210534</t>
+          <t>281483</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>324229</t>
+          <t>332229</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>431208</t>
+          <t>470591</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>340825</t>
+          <t>434883</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>488322</t>
+          <t>512865</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2140870</t>
+          <t>2067136</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2111473</t>
+          <t>2040031</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2190585</t>
+          <t>2088708</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1956073</t>
+          <t>1864231</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1913594</t>
+          <t>1839163</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2027289</t>
+          <t>1889909</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4096942</t>
+          <t>3931368</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4039828</t>
+          <t>3889094</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4187325</t>
+          <t>3967076</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>39327</t>
+          <t>40958</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29474</t>
+          <t>29913</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53606</t>
+          <t>54393</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>58597</t>
+          <t>64569</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46844</t>
+          <t>52688</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71056</t>
+          <t>78290</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>97924</t>
+          <t>105527</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82377</t>
+          <t>89710</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115503</t>
+          <t>124034</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>607296</t>
+          <t>670629</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>593017</t>
+          <t>657194</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>617149</t>
+          <t>681674</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>601866</t>
+          <t>670308</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>589407</t>
+          <t>656587</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>613619</t>
+          <t>682189</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1209162</t>
+          <t>1340937</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1191583</t>
+          <t>1322430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1224709</t>
+          <t>1356754</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>282602</t>
+          <t>305311</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>217547</t>
+          <t>274973</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>319352</t>
+          <t>339911</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>601452</t>
+          <t>651804</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>483402</t>
+          <t>612139</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>655027</t>
+          <t>690130</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>884054</t>
+          <t>957114</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>765729</t>
+          <t>906101</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>956560</t>
+          <t>1004505</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3169287</t>
+          <t>3215372</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3132537</t>
+          <t>3180772</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3234342</t>
+          <t>3245710</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3052342</t>
+          <t>3076503</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2998767</t>
+          <t>3038177</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3170392</t>
+          <t>3116168</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6221629</t>
+          <t>6291876</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6149123</t>
+          <t>6244485</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6339954</t>
+          <t>6342889</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>87,5%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
